--- a/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0152.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0152.xlsx
@@ -704,7 +704,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Chuyện gì đã xảy ra?</t>
+          <t>Chuyện gì đã xảy ra thế?</t>
         </is>
       </c>
     </row>
@@ -899,7 +899,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Cho cô ấy thấy sức mạnh của cậu đi!</t>
+          <t>Cho cô ấy thấy sức mạnh của mày đi!</t>
         </is>
       </c>
     </row>
@@ -1744,7 +1744,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Ta hiểu ý ngươi rồi. Lần trước mua đồ của lão thương nhân Banagher kia, toàn đồ cũ đóng gói lại thôi.</t>
+          <t>Tao hiểu ý mày rồi. Lần trước mua đồ của lão thương nhân Banagher kia, toàn đồ cũ đóng gói lại thôi.</t>
         </is>
       </c>
     </row>
@@ -2979,7 +2979,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>Hừ. Toàn lời bao biện. Ta hiểu rồi. Chẳng qua là vì tiền, phải không?</t>
+          <t>Hừ. Toàn lời bao biện. Tao hiểu rồi. Chẳng qua là vì tiền, phải không?</t>
         </is>
       </c>
     </row>
@@ -3109,7 +3109,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>Luật lệ, luật lệ... lúc nào cũng toàn luật lệ! Cuối cùng ta cũng kiếm được chút tiền, chỉ muốn hưởng thụ thôi mà, có quá đáng không?</t>
+          <t>Luật lệ, luật lệ... lúc nào cũng toàn luật lệ! Cuối cùng tao cũng kiếm được chút tiền, chỉ muốn hưởng thụ thôi mà, có quá đáng không?</t>
         </is>
       </c>
     </row>
@@ -3369,7 +3369,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>Xin lỗi, cậu có thể dành cho tôi chút thời gian không?</t>
+          <t>Xin lỗi, bạn có thể dành cho tôi chút thời gian không?</t>
         </is>
       </c>
     </row>
@@ -4799,7 +4799,7 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>Phải, ta là Stav. Trời ạ, nghe cái danh xưng đó mỗi lần lại thấy ngượng chết đi được...</t>
+          <t>Phải, tao là Stav. Trời ạ, nghe cái danh xưng đó mỗi lần lại thấy ngượng chết đi được...</t>
         </is>
       </c>
     </row>
@@ -4929,7 +4929,7 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>Đấu sĩ huyền thoại Stav. Người ba lần lọt vào chung kết. Không thể tin được là cuối cùng ta cũng được gặp mặt ông!</t>
+          <t>Đấu sĩ huyền thoại Stav. Người ba lần lọt vào chung kết. Không thể tin được là cuối cùng tao cũng được gặp mặt ông!</t>
         </is>
       </c>
     </row>
@@ -5449,7 +5449,7 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>Yes.</t>
+          <t>Đúng vậy.</t>
         </is>
       </c>
     </row>
@@ -6684,7 +6684,7 @@
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>Và có lần bố cậu để ta tắm trước, còn đợi ta ở ngoài lâu lắm.</t>
+          <t>Và có lần bố cậu để tao tắm trước, còn đợi tao ở ngoài lâu lắm.</t>
         </is>
       </c>
     </row>
@@ -6749,7 +6749,7 @@
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>Suối Nước Nóng Thermes quả thật xứng danh. Nội thất đẹp đến mê hồn, trải nghiệm như trong mơ... Ta mà được thì ngâm mình ở đây 24/7 luôn.</t>
+          <t>Suối Nước Nóng Thermes quả thật xứng danh. Nội thất đẹp đến mê hồn, trải nghiệm như trong mơ... Tao mà được thì ngâm mình ở đây 24/7 luôn.</t>
         </is>
       </c>
     </row>
@@ -7529,7 +7529,7 @@
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>Yes.</t>
+          <t>Đúng vậy.</t>
         </is>
       </c>
     </row>
@@ -8114,7 +8114,7 @@
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>Ta đã bảo rồi, dồn hết vào Lupa đi, ngươi sẽ thắng lớn! Lupa the Dupa. Cô ấy là nhất đấy!</t>
+          <t>Tao đã bảo rồi, dồn hết vào Lupa đi, mày sẽ thắng lớn! Lupa the Dupa. Cô ấy là nhất đấy!</t>
         </is>
       </c>
     </row>
@@ -8244,7 +8244,7 @@
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>Ta thậm chí không cần xem mấy trận đấu của cô ấy cũng biết kết quả thế nào. Sáng thức dậy là bùm! Thắng thêm một trận nữa rồi!</t>
+          <t>Tao thậm chí không cần xem mấy trận đấu của cô ấy cũng biết kết quả thế nào. Sáng thức dậy là bùm! Thắng thêm một trận nữa rồi!</t>
         </is>
       </c>
     </row>
@@ -10909,7 +10909,7 @@
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t>Nguyền rủa thật đấy. Năm nay vận đen của ta đúng là khác. Đến cả Agon ta cũng chẳng vào nổi...</t>
+          <t>Nguyền rủa thật đấy. Năm nay vận đen của tao đúng là khác. Đến cả Agon tao cũng chẳng vào nổi...</t>
         </is>
       </c>
     </row>
@@ -12534,7 +12534,7 @@
       </c>
       <c r="M186" t="inlineStr">
         <is>
-          <t>Ta đã bảo rồi, hắn là quý tộc. Những kẻ có đặc quyền đâu phải xếp hàng, chúng vào thẳng phòng VIP. Đặc quyền, ngươi chưa nghe bao giờ à?</t>
+          <t>Tao đã bảo rồi, hắn là quý tộc. Những kẻ có đặc quyền đâu phải xếp hàng, chúng vào thẳng phòng VIP. Đặc quyền, mày chưa nghe bao giờ à?</t>
         </is>
       </c>
     </row>
@@ -12729,7 +12729,7 @@
       </c>
       <c r="M189" t="inlineStr">
         <is>
-          <t>Đặc quyền à? Tại sao hắn lại được đi thẳng vào trong khi ta phải xếp hàng ngoài nắng thế này? Chẳng có lấy một bóng râm!</t>
+          <t>Đặc quyền à? Tại sao hắn lại được đi thẳng vào trong khi tao phải xếp hàng ngoài nắng thế này? Chẳng có lấy một bóng râm!</t>
         </is>
       </c>
     </row>
@@ -12924,7 +12924,7 @@
       </c>
       <c r="M192" t="inlineStr">
         <is>
-          <t>Dù ngươi có cố gây sự với hắn đi chăng nữa, cũng phải vượt qua cả đám đấu sĩ chuyên nghiệp trong túi tiền của nhà hắn đã, mới mong gặp được mặt thằng cha ấy.</t>
+          <t>Dù mày có cố gây sự với hắn đi chăng nữa, cũng phải vượt qua cả đám đấu sĩ chuyên nghiệp trong túi tiền của nhà hắn đã, mới mong gặp được mặt thằng cha ấy.</t>
         </is>
       </c>
     </row>
@@ -13119,7 +13119,7 @@
       </c>
       <c r="M195" t="inlineStr">
         <is>
-          <t>Cậu lảm nhảm cái gì thế? Tắm nhiều nước vào đầu à?</t>
+          <t>Mày lảm nhảm cái gì thế? Tắm nhiều nước vào đầu à?</t>
         </is>
       </c>
     </row>
@@ -13444,7 +13444,7 @@
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t>Ugh, ta không nghĩ mình làm được đâu.</t>
+          <t>Ugh, tao không nghĩ mình làm được đâu.</t>
         </is>
       </c>
     </row>
@@ -13899,7 +13899,7 @@
       </c>
       <c r="M207" t="inlineStr">
         <is>
-          <t>Ồ, "anh hùng" à? Ngươi nghĩ ta là ai hả?!</t>
+          <t>Ồ, "anh hùng" à? Mày nghĩ tao là ai hả?!</t>
         </is>
       </c>
     </row>
@@ -14419,7 +14419,7 @@
       </c>
       <c r="M215" t="inlineStr">
         <is>
-          <t>Đồ khốn... Ta định bán chúng trong Đại Khổ Nạn mà. Giờ thì toi hết rồi...</t>
+          <t>Đồ khốn... Tao định bán chúng trong Đại Khổ Nạn mà. Giờ thì toi hết rồi...</t>
         </is>
       </c>
     </row>
@@ -16174,7 +16174,7 @@
       </c>
       <c r="M242" t="inlineStr">
         <is>
-          <t>Ta phải lặp lại bao nhiêu lần nữa hả? Những kẻ truyền giáo của Giáo Đoàn Vực Sâu bị cấm vào Septimont.</t>
+          <t>Tao phải lặp lại bao nhiêu lần nữa hả? Những kẻ truyền giáo của Giáo Đoàn Vực Sâu bị cấm vào Septimont.</t>
         </is>
       </c>
     </row>
@@ -17214,7 +17214,7 @@
       </c>
       <c r="M258" t="inlineStr">
         <is>
-          <t>Để ta đi qua được không? Ta sắp thi đấu rồi, muộn mất!</t>
+          <t>Để tao đi qua được không? Tao sắp thi đấu rồi, muộn mất!</t>
         </is>
       </c>
     </row>
@@ -17734,7 +17734,7 @@
       </c>
       <c r="M266" t="inlineStr">
         <is>
-          <t>Nghe nặng nhọc quá... mà ta vừa tan ca đêm, giờ lại phải làm thêm nguyên ngày cho ngươi nữa à...</t>
+          <t>Nghe nặng nhọc quá... mà tao vừa tan ca đêm, giờ lại phải làm thêm nguyên ngày cho mày nữa à...</t>
         </is>
       </c>
     </row>
@@ -18124,7 +18124,7 @@
       </c>
       <c r="M272" t="inlineStr">
         <is>
-          <t>&lt;i&gt;DVD lậu Feilian Beringal vs. Inferno Rider? Dầu thơm Order of the Deep-scented?&lt;/i&gt;</t>
+          <t>&lt;i&gt;DVD lậu Feilian Beringal vs. Inferno Rider? Dầu thơm Order of the Deep-scented?&lt;i&gt;</t>
         </is>
       </c>
     </row>
@@ -20789,7 +20789,7 @@
       </c>
       <c r="M313" t="inlineStr">
         <is>
-          <t>Tên đấu sĩ kia trông như cần giúp đỡ, nhưng cách nó tự nói chuyện với bản thân làm ta phát ớn...</t>
+          <t>Tên đấu sĩ kia trông như cần giúp đỡ, nhưng cách nó tự nói chuyện với bản thân làm tao phát ớn...</t>
         </is>
       </c>
     </row>
@@ -20854,7 +20854,7 @@
       </c>
       <c r="M314" t="inlineStr">
         <is>
-          <t>Chào cậu, hàng đợi làm thủ tục hải quan... Ủa? Có chuyện gì thế? Cậu có gì muốn báo cáo không?</t>
+          <t>Chào bạn, hàng đợi làm thủ tục hải quan... Ủa? Có chuyện gì thế? bạn có gì muốn báo cáo không?</t>
         </is>
       </c>
     </row>
@@ -21244,7 +21244,7 @@
       </c>
       <c r="M320" t="inlineStr">
         <is>
-          <t>Sau khi anh nhắc về tần số bất thường, chúng tôi đã nhờ một Cộng Hưởng Giả kiểm tra kỹ những thùng hàng đó.</t>
+          <t>Sau khi anh nhắc về tần số bất thường, chúng tôi đã nhờ một Resonator kiểm tra kỹ những thùng hàng đó.</t>
         </is>
       </c>
     </row>
@@ -21439,7 +21439,7 @@
       </c>
       <c r="M323" t="inlineStr">
         <is>
-          <t>Đồ khốn... Ta định bán chúng trong Đại Khổ Nạn mà. Giờ thì toi hết rồi...</t>
+          <t>Đồ khốn... Tao định bán chúng trong Đại Khổ Nạn mà. Giờ thì toi hết rồi...</t>
         </is>
       </c>
     </row>
@@ -21764,7 +21764,7 @@
       </c>
       <c r="M328" t="inlineStr">
         <is>
-          <t>Chào cậu, hàng đợi làm thủ tục hải quan... Ủa? Có chuyện gì thế? Cậu có gì muốn báo cáo không?</t>
+          <t>Chào bạn, hàng đợi làm thủ tục hải quan... Ủa? Có chuyện gì thế? bạn có gì muốn báo cáo không?</t>
         </is>
       </c>
     </row>
@@ -22024,7 +22024,7 @@
       </c>
       <c r="M332" t="inlineStr">
         <is>
-          <t>Tần số à? Vậy à? Hiểu rồi. Có vẻ chúng ta cần tìm một Cộng Hưởng Giả để đóng vai thanh tra.</t>
+          <t>Tần số à? Vậy à? Hiểu rồi. Có vẻ chúng ta cần tìm một Resonator để đóng vai thanh tra.</t>
         </is>
       </c>
     </row>
